--- a/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_CBQ.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_CBQ.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
         <v>16</v>
